--- a/Eka_Report_back/ProductionReport_R3.xlsx
+++ b/Eka_Report_back/ProductionReport_R3.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\new\Eka_Report\Eka_Report_back\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F9C3E2-EDA3-4910-97AE-5AF3FEEECBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prod Report" sheetId="1" r:id="rId1"/>
@@ -47,7 +48,7 @@
     <definedName name="YTD_C21_F22">#REF!</definedName>
     <definedName name="YTD_C31_F32">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -63,13 +64,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>DELL</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -84,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R2" authorId="1" shapeId="0">
+    <comment ref="R2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -99,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="1" shapeId="0">
+    <comment ref="R3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -114,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="1" shapeId="0">
+    <comment ref="R4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -129,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="1" shapeId="0">
+    <comment ref="E10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -144,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="1" shapeId="0">
+    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -159,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H10" authorId="1" shapeId="0">
+    <comment ref="H10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -174,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="1" shapeId="0">
+    <comment ref="M10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -189,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N10" authorId="1" shapeId="0">
+    <comment ref="N10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -204,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P10" authorId="1" shapeId="0">
+    <comment ref="P10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -219,7 +220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="1" shapeId="0">
+    <comment ref="E19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -234,7 +235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F19" authorId="1" shapeId="0">
+    <comment ref="F19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -249,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="1" shapeId="0">
+    <comment ref="H19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -264,7 +265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M19" authorId="1" shapeId="0">
+    <comment ref="M19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -279,7 +280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N19" authorId="1" shapeId="0">
+    <comment ref="N19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -294,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P19" authorId="1" shapeId="0">
+    <comment ref="P19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -309,7 +310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="1" shapeId="0">
+    <comment ref="E27" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -324,7 +325,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F27" authorId="1" shapeId="0">
+    <comment ref="F27" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
         <r>
           <rPr>
@@ -339,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="1" shapeId="0">
+    <comment ref="H27" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
         <r>
           <rPr>
@@ -354,7 +355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M27" authorId="1" shapeId="0">
+    <comment ref="M27" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
         <r>
           <rPr>
@@ -369,7 +370,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N27" authorId="1" shapeId="0">
+    <comment ref="N27" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
       <text>
         <r>
           <rPr>
@@ -384,7 +385,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P27" authorId="1" shapeId="0">
+    <comment ref="P27" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -399,7 +400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E32" authorId="1" shapeId="0">
+    <comment ref="E32" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
       <text>
         <r>
           <rPr>
@@ -414,7 +415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="1" shapeId="0">
+    <comment ref="E35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
       <text>
         <r>
           <rPr>
@@ -429,7 +430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="1" shapeId="0">
+    <comment ref="F35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
       <text>
         <r>
           <rPr>
@@ -444,7 +445,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G35" authorId="1" shapeId="0">
+    <comment ref="G35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -459,7 +460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H35" authorId="1" shapeId="0">
+    <comment ref="H35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -474,7 +475,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="1" shapeId="0">
+    <comment ref="I35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -489,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J35" authorId="1" shapeId="0">
+    <comment ref="J35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -504,7 +505,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K35" authorId="1" shapeId="0">
+    <comment ref="K35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -519,7 +520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L35" authorId="1" shapeId="0">
+    <comment ref="L35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -534,7 +535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M35" authorId="1" shapeId="0">
+    <comment ref="M35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020000000}">
       <text>
         <r>
           <rPr>
@@ -549,7 +550,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N35" authorId="1" shapeId="0">
+    <comment ref="N35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021000000}">
       <text>
         <r>
           <rPr>
@@ -564,7 +565,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O35" authorId="1" shapeId="0">
+    <comment ref="O35" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022000000}">
       <text>
         <r>
           <rPr>
@@ -584,12 +585,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -605,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D2" authorId="0" shapeId="0">
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -621,7 +622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E2" authorId="0" shapeId="0">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -637,7 +638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -653,7 +654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L2" authorId="0" shapeId="0">
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -669,7 +670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="0" shapeId="0">
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -685,7 +686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -699,7 +700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0" shapeId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -713,7 +714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -727,7 +728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -741,7 +742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -755,7 +756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0" shapeId="0">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -769,7 +770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -785,7 +786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0">
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -801,7 +802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -817,7 +818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0">
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
       <text>
         <r>
           <rPr>
@@ -833,7 +834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C13" authorId="0" shapeId="0">
+    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000011000000}">
       <text>
         <r>
           <rPr>
@@ -847,7 +848,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0" shapeId="0">
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000012000000}">
       <text>
         <r>
           <rPr>
@@ -861,7 +862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0">
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000013000000}">
       <text>
         <r>
           <rPr>
@@ -875,7 +876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000014000000}">
       <text>
         <r>
           <rPr>
@@ -889,7 +890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C21" authorId="0" shapeId="0">
+    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000015000000}">
       <text>
         <r>
           <rPr>
@@ -905,7 +906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D21" authorId="0" shapeId="0">
+    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000016000000}">
       <text>
         <r>
           <rPr>
@@ -921,7 +922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000017000000}">
       <text>
         <r>
           <rPr>
@@ -937,7 +938,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
+    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000018000000}">
       <text>
         <r>
           <rPr>
@@ -953,7 +954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C22" authorId="0" shapeId="0">
+    <comment ref="C22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000019000000}">
       <text>
         <r>
           <rPr>
@@ -967,7 +968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D22" authorId="0" shapeId="0">
+    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -981,7 +982,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E22" authorId="0" shapeId="0">
+    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -995,7 +996,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
+    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -1009,7 +1010,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C31" authorId="0" shapeId="0">
+    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -1025,7 +1026,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D31" authorId="0" shapeId="0">
+    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -1041,7 +1042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E31" authorId="0" shapeId="0">
+    <comment ref="E31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -1057,7 +1058,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F31" authorId="0" shapeId="0">
+    <comment ref="F31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000020000000}">
       <text>
         <r>
           <rPr>
@@ -1073,7 +1074,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C32" authorId="0" shapeId="0">
+    <comment ref="C32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000021000000}">
       <text>
         <r>
           <rPr>
@@ -1087,7 +1088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D32" authorId="0" shapeId="0">
+    <comment ref="D32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000022000000}">
       <text>
         <r>
           <rPr>
@@ -1101,7 +1102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E32" authorId="0" shapeId="0">
+    <comment ref="E32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000023000000}">
       <text>
         <r>
           <rPr>
@@ -1115,7 +1116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F32" authorId="0" shapeId="0">
+    <comment ref="F32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000024000000}">
       <text>
         <r>
           <rPr>
@@ -1337,7 +1338,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -1377,18 +1378,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1814,7 +1809,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1831,121 +1826,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1954,67 +1887,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2024,26 +1987,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2063,7 +2050,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Prod Report"/>
@@ -2201,9 +2188,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2241,9 +2228,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2278,7 +2265,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2313,7 +2300,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2486,1362 +2473,1289 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="12" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="12" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="12" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="12" customWidth="1"/>
-    <col min="8" max="8" width="12" style="12" customWidth="1"/>
-    <col min="9" max="9" width="14" style="12" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="6" style="12" customWidth="1"/>
-    <col min="12" max="12" width="6.140625" style="12" customWidth="1"/>
-    <col min="13" max="13" width="6" style="12" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" style="12" customWidth="1"/>
-    <col min="15" max="15" width="6.85546875" style="12" customWidth="1"/>
-    <col min="16" max="16" width="6" style="12" customWidth="1"/>
-    <col min="17" max="18" width="6.5703125" style="12" customWidth="1"/>
-    <col min="19" max="19" width="6.140625" style="12" customWidth="1"/>
-    <col min="20" max="20" width="5" style="12" customWidth="1"/>
-    <col min="21" max="21" width="8.7109375" style="12" customWidth="1"/>
-    <col min="22" max="23" width="9" style="12"/>
-    <col min="24" max="24" width="32.28515625" style="12" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="12"/>
+    <col min="1" max="1" width="8.5546875" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="6.109375" customWidth="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="6.6640625" customWidth="1"/>
+    <col min="15" max="15" width="6.88671875" customWidth="1"/>
+    <col min="16" max="16" width="6" customWidth="1"/>
+    <col min="17" max="18" width="6.5546875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5" customWidth="1"/>
+    <col min="21" max="21" width="8.6640625" customWidth="1"/>
+    <col min="24" max="24" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15" customHeight="1" thickBot="1"/>
     <row r="2" spans="1:21" ht="15" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="83" t="s">
+      <c r="C2" s="64"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="86" t="s">
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="86"/>
-      <c r="T2" s="15"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="12"/>
       <c r="U2" s="3"/>
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="76">
+      <c r="B3" s="75">
         <v>0.69398981410879634</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="90" t="s">
+      <c r="C3" s="61"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="70"/>
+      <c r="N3" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="91"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="92"/>
-      <c r="R3" s="28">
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="79">
         <v>26</v>
       </c>
-      <c r="S3" s="28"/>
-      <c r="T3" s="10"/>
+      <c r="S3" s="79"/>
       <c r="U3" s="6"/>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="4"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="90" t="s">
+      <c r="N4" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="91"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="28">
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="79">
         <v>18</v>
       </c>
-      <c r="S4" s="28"/>
-      <c r="T4" s="10"/>
+      <c r="S4" s="79"/>
       <c r="U4" s="6"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="4"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="18"/>
       <c r="U5" s="6"/>
     </row>
-    <row r="6" spans="1:21" ht="15.75">
-      <c r="A6" s="30" t="s">
+    <row r="6" spans="1:21" ht="15.6">
+      <c r="A6" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="18"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="1"/>
       <c r="U6" s="6"/>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="44"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="38" t="s">
+      <c r="A7" s="60"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="38" t="s">
+      <c r="F7" s="38"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="38" t="s">
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="N7" s="45"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="38" t="s">
+      <c r="N7" s="38"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38" t="s">
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="S7" s="38"/>
-      <c r="T7" s="22"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="18"/>
       <c r="U7" s="5"/>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="48"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="27" t="s">
+      <c r="A8" s="62"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="38" t="s">
+      <c r="F8" s="38"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="27" t="s">
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="45"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="38" t="s">
+      <c r="N8" s="38"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38" t="str">
+      <c r="Q8" s="45"/>
+      <c r="R8" s="45" t="str">
         <f>[1]PrevFY!C12</f>
         <v>25-26</v>
       </c>
-      <c r="S8" s="38"/>
-      <c r="T8" s="22"/>
+      <c r="S8" s="45"/>
+      <c r="T8" s="18"/>
       <c r="U8" s="5"/>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="11" t="s">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="38" t="s">
+      <c r="P9" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38" t="s">
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="S9" s="38"/>
-      <c r="T9" s="22"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="18"/>
       <c r="U9" s="5"/>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="19">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="15">
         <v>70</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="15">
         <v>23</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="15">
         <v>-47</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="15">
         <v>15</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="15">
         <v>8</v>
       </c>
-      <c r="J10" s="19">
-        <v>0</v>
-      </c>
-      <c r="K10" s="19">
-        <v>0</v>
-      </c>
-      <c r="L10" s="19">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
+      <c r="J10" s="15">
+        <v>0</v>
+      </c>
+      <c r="K10" s="15">
+        <v>0</v>
+      </c>
+      <c r="L10" s="15">
+        <v>0</v>
+      </c>
+      <c r="M10" s="15">
         <v>10</v>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="15">
         <v>2</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="15">
         <v>-8</v>
       </c>
-      <c r="P10" s="35">
+      <c r="P10" s="91">
         <v>288</v>
       </c>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35">
+      <c r="Q10" s="91"/>
+      <c r="R10" s="91">
         <v>68</v>
       </c>
-      <c r="S10" s="35"/>
-      <c r="T10" s="22"/>
+      <c r="S10" s="91"/>
+      <c r="T10" s="18"/>
       <c r="U10" s="5"/>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="19">
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="15">
         <v>80</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="15">
         <v>29</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="15">
         <v>-51</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="15">
         <v>24</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="15">
         <v>5</v>
       </c>
-      <c r="J11" s="19">
-        <v>0</v>
-      </c>
-      <c r="K11" s="19">
-        <v>0</v>
-      </c>
-      <c r="L11" s="19">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9">
+      <c r="J11" s="15">
+        <v>0</v>
+      </c>
+      <c r="K11" s="15">
+        <v>0</v>
+      </c>
+      <c r="L11" s="15">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15">
         <v>10</v>
       </c>
-      <c r="N11" s="9">
+      <c r="N11" s="15">
         <v>1</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="15">
         <v>-9</v>
       </c>
-      <c r="P11" s="35">
+      <c r="P11" s="91">
         <v>366</v>
       </c>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35">
+      <c r="Q11" s="91"/>
+      <c r="R11" s="91">
         <v>68</v>
       </c>
-      <c r="S11" s="35"/>
-      <c r="T11" s="22"/>
+      <c r="S11" s="91"/>
+      <c r="T11" s="18"/>
       <c r="U11" s="5"/>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="20">
-        <v>0</v>
-      </c>
-      <c r="F12" s="20">
-        <v>0</v>
-      </c>
-      <c r="G12" s="20">
-        <v>0</v>
-      </c>
-      <c r="H12" s="20">
-        <v>0</v>
-      </c>
-      <c r="I12" s="20">
-        <v>0</v>
-      </c>
-      <c r="J12" s="20">
-        <v>0</v>
-      </c>
-      <c r="K12" s="20">
-        <v>0</v>
-      </c>
-      <c r="L12" s="20">
-        <v>0</v>
-      </c>
-      <c r="M12" s="20">
-        <v>0</v>
-      </c>
-      <c r="N12" s="20">
-        <v>0</v>
-      </c>
-      <c r="O12" s="20">
-        <v>0</v>
-      </c>
-      <c r="P12" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="36">
-        <v>0</v>
-      </c>
-      <c r="S12" s="37"/>
-      <c r="T12" s="22"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="16">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0</v>
+      </c>
+      <c r="H12" s="16">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16">
+        <v>0</v>
+      </c>
+      <c r="J12" s="16">
+        <v>0</v>
+      </c>
+      <c r="K12" s="16">
+        <v>0</v>
+      </c>
+      <c r="L12" s="16">
+        <v>0</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0</v>
+      </c>
+      <c r="N12" s="16">
+        <v>0</v>
+      </c>
+      <c r="O12" s="16">
+        <v>0</v>
+      </c>
+      <c r="P12" s="92">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="93"/>
+      <c r="R12" s="92">
+        <v>0</v>
+      </c>
+      <c r="S12" s="93"/>
+      <c r="T12" s="18"/>
       <c r="U12" s="5"/>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="20">
-        <v>0</v>
-      </c>
-      <c r="F13" s="20">
-        <v>0</v>
-      </c>
-      <c r="G13" s="20">
-        <v>0</v>
-      </c>
-      <c r="H13" s="20">
-        <v>0</v>
-      </c>
-      <c r="I13" s="20">
-        <v>0</v>
-      </c>
-      <c r="J13" s="20">
-        <v>0</v>
-      </c>
-      <c r="K13" s="20">
-        <v>0</v>
-      </c>
-      <c r="L13" s="20">
-        <v>0</v>
-      </c>
-      <c r="M13" s="20">
-        <v>0</v>
-      </c>
-      <c r="N13" s="20">
-        <v>0</v>
-      </c>
-      <c r="O13" s="20">
-        <v>0</v>
-      </c>
-      <c r="P13" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="36">
-        <v>0</v>
-      </c>
-      <c r="S13" s="37"/>
-      <c r="T13" s="22"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
+        <v>0</v>
+      </c>
+      <c r="J13" s="16">
+        <v>0</v>
+      </c>
+      <c r="K13" s="16">
+        <v>0</v>
+      </c>
+      <c r="L13" s="16">
+        <v>0</v>
+      </c>
+      <c r="M13" s="16">
+        <v>0</v>
+      </c>
+      <c r="N13" s="16">
+        <v>0</v>
+      </c>
+      <c r="O13" s="16">
+        <v>0</v>
+      </c>
+      <c r="P13" s="92">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="93"/>
+      <c r="R13" s="92">
+        <v>0</v>
+      </c>
+      <c r="S13" s="93"/>
+      <c r="T13" s="18"/>
       <c r="U13" s="5"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="4"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="22"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="18"/>
       <c r="U14" s="5"/>
     </row>
-    <row r="15" spans="1:21" ht="15.75">
-      <c r="A15" s="30" t="s">
+    <row r="15" spans="1:21" ht="15.6">
+      <c r="A15" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="18"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="47"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="1"/>
       <c r="U15" s="6"/>
     </row>
     <row r="16" spans="1:21">
-      <c r="A16" s="52"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="34" t="s">
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="34" t="s">
+      <c r="F16" s="27"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="34" t="s">
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N16" s="40"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="34" t="s">
+      <c r="N16" s="27"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34" t="s">
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="S16" s="34"/>
-      <c r="T16" s="18"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="1"/>
       <c r="U16" s="6"/>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="54"/>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="42" t="s">
+      <c r="A17" s="50"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="34" t="s">
+      <c r="F17" s="27"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="I17" s="40"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="40"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="42" t="s">
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="N17" s="40"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="18"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="1"/>
       <c r="U17" s="6"/>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="21" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="H18" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="21" t="s">
+      <c r="I18" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="J18" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="K18" s="21" t="s">
+      <c r="K18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="L18" s="21" t="s">
+      <c r="L18" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="21" t="s">
+      <c r="M18" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="N18" s="21" t="s">
+      <c r="N18" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O18" s="21" t="s">
+      <c r="O18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="P18" s="34" t="s">
+      <c r="P18" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34" t="s">
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S18" s="34"/>
-      <c r="T18" s="17"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="14"/>
       <c r="U18" s="7"/>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="19">
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="15">
         <v>70</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="15">
         <v>23</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="15">
         <v>-47</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="15">
         <v>15</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="15">
         <v>8</v>
       </c>
-      <c r="J19" s="19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="19">
-        <v>0</v>
-      </c>
-      <c r="L19" s="19">
-        <v>0</v>
-      </c>
-      <c r="M19" s="9">
+      <c r="J19" s="15">
+        <v>0</v>
+      </c>
+      <c r="K19" s="15">
+        <v>0</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0</v>
+      </c>
+      <c r="M19" s="15">
         <v>10</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="15">
         <v>2</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="15">
         <v>-8</v>
       </c>
-      <c r="P19" s="35">
+      <c r="P19" s="91">
         <v>288</v>
       </c>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35">
+      <c r="Q19" s="91"/>
+      <c r="R19" s="91">
         <v>68</v>
       </c>
-      <c r="S19" s="35"/>
-      <c r="T19" s="10"/>
+      <c r="S19" s="91"/>
       <c r="U19" s="5"/>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="20">
-        <v>0</v>
-      </c>
-      <c r="G20" s="20">
-        <v>0</v>
-      </c>
-      <c r="H20" s="20">
-        <v>0</v>
-      </c>
-      <c r="I20" s="20">
-        <v>0</v>
-      </c>
-      <c r="J20" s="20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="20">
-        <v>0</v>
-      </c>
-      <c r="L20" s="20">
-        <v>0</v>
-      </c>
-      <c r="M20" s="20">
-        <v>0</v>
-      </c>
-      <c r="N20" s="20">
-        <v>0</v>
-      </c>
-      <c r="O20" s="20">
-        <v>0</v>
-      </c>
-      <c r="P20" s="93" t="s">
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="16">
+        <v>0</v>
+      </c>
+      <c r="F20" s="16">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16">
+        <v>0</v>
+      </c>
+      <c r="H20" s="16">
+        <v>0</v>
+      </c>
+      <c r="I20" s="16">
+        <v>0</v>
+      </c>
+      <c r="J20" s="16">
+        <v>0</v>
+      </c>
+      <c r="K20" s="16">
+        <v>0</v>
+      </c>
+      <c r="L20" s="16">
+        <v>0</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0</v>
+      </c>
+      <c r="N20" s="16">
+        <v>0</v>
+      </c>
+      <c r="O20" s="16">
+        <v>0</v>
+      </c>
+      <c r="P20" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="93" t="s">
+      <c r="Q20" s="91"/>
+      <c r="R20" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="S20" s="35"/>
-      <c r="T20" s="10"/>
+      <c r="S20" s="91"/>
       <c r="U20" s="5"/>
     </row>
     <row r="21" spans="1:21">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="20">
-        <v>0</v>
-      </c>
-      <c r="F21" s="20">
-        <v>0</v>
-      </c>
-      <c r="G21" s="20">
-        <v>0</v>
-      </c>
-      <c r="H21" s="20">
-        <v>0</v>
-      </c>
-      <c r="I21" s="20">
-        <v>0</v>
-      </c>
-      <c r="J21" s="20">
-        <v>0</v>
-      </c>
-      <c r="K21" s="20">
-        <v>0</v>
-      </c>
-      <c r="L21" s="20">
-        <v>0</v>
-      </c>
-      <c r="M21" s="20">
-        <v>0</v>
-      </c>
-      <c r="N21" s="20">
-        <v>0</v>
-      </c>
-      <c r="O21" s="20">
-        <v>0</v>
-      </c>
-      <c r="P21" s="29">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="29">
-        <v>0</v>
-      </c>
-      <c r="S21" s="29"/>
-      <c r="T21" s="10"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="16">
+        <v>0</v>
+      </c>
+      <c r="F21" s="16">
+        <v>0</v>
+      </c>
+      <c r="G21" s="16">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <v>0</v>
+      </c>
+      <c r="I21" s="16">
+        <v>0</v>
+      </c>
+      <c r="J21" s="16">
+        <v>0</v>
+      </c>
+      <c r="K21" s="16">
+        <v>0</v>
+      </c>
+      <c r="L21" s="16">
+        <v>0</v>
+      </c>
+      <c r="M21" s="16">
+        <v>0</v>
+      </c>
+      <c r="N21" s="16">
+        <v>0</v>
+      </c>
+      <c r="O21" s="16">
+        <v>0</v>
+      </c>
+      <c r="P21" s="95">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="95"/>
+      <c r="R21" s="95">
+        <v>0</v>
+      </c>
+      <c r="S21" s="95"/>
       <c r="U21" s="5"/>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
-      <c r="S22" s="25"/>
-      <c r="T22" s="10"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="21"/>
       <c r="U22" s="5"/>
     </row>
-    <row r="23" spans="1:21" ht="15.75">
-      <c r="A23" s="32" t="s">
+    <row r="23" spans="1:21" ht="15.6">
+      <c r="A23" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="18"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="90"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="90"/>
+      <c r="R23" s="90"/>
+      <c r="S23" s="90"/>
+      <c r="T23" s="1"/>
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="52"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="34" t="s">
+      <c r="A24" s="48"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="34" t="s">
+      <c r="F24" s="27"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="34" t="s">
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N24" s="40"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="34" t="s">
+      <c r="N24" s="27"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34" t="s">
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="S24" s="34"/>
-      <c r="T24" s="18"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="1"/>
       <c r="U24" s="6"/>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="54"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="42" t="s">
+      <c r="A25" s="50"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="34" t="s">
+      <c r="F25" s="27"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="42" t="s">
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="N25" s="40"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="34">
+      <c r="N25" s="27"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="25">
         <f>[1]YTD!C29</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="34"/>
-      <c r="R25" s="34">
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25">
         <f>[1]PrevFY!C29</f>
         <v>0</v>
       </c>
-      <c r="S25" s="34"/>
-      <c r="T25" s="18"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="1"/>
       <c r="U25" s="6"/>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="21" t="s">
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="F26" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="G26" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="21" t="s">
+      <c r="H26" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="21" t="s">
+      <c r="I26" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J26" s="21" t="s">
+      <c r="J26" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="21" t="s">
+      <c r="K26" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="21" t="s">
+      <c r="L26" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="M26" s="21" t="s">
+      <c r="M26" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="N26" s="21" t="s">
+      <c r="N26" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="O26" s="21" t="s">
+      <c r="O26" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="P26" s="34" t="s">
+      <c r="P26" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34" t="s">
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="S26" s="34"/>
-      <c r="T26" s="17"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="14"/>
       <c r="U26" s="7"/>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="94" t="s">
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F27" s="94" t="s">
+      <c r="F27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G27" s="94" t="s">
+      <c r="G27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="H27" s="94" t="s">
+      <c r="H27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="I27" s="94" t="s">
+      <c r="I27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="J27" s="94" t="s">
+      <c r="J27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="K27" s="94" t="s">
+      <c r="K27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="L27" s="94" t="s">
+      <c r="L27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="M27" s="94" t="s">
+      <c r="M27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="N27" s="94" t="s">
+      <c r="N27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="O27" s="94" t="s">
+      <c r="O27" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="P27" s="93" t="s">
+      <c r="P27" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="93" t="s">
+      <c r="Q27" s="91"/>
+      <c r="R27" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="S27" s="35"/>
-      <c r="T27" s="10"/>
+      <c r="S27" s="91"/>
       <c r="U27" s="5"/>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="39" t="s">
+      <c r="A28" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="94" t="s">
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="94" t="s">
+      <c r="F28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="94" t="s">
+      <c r="G28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="H28" s="94" t="s">
+      <c r="H28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="I28" s="94" t="s">
+      <c r="I28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="J28" s="94" t="s">
+      <c r="J28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="K28" s="94" t="s">
+      <c r="K28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="L28" s="94" t="s">
+      <c r="L28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="M28" s="94" t="s">
+      <c r="M28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="N28" s="94" t="s">
+      <c r="N28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="O28" s="94" t="s">
+      <c r="O28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="P28" s="93" t="s">
+      <c r="P28" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="93" t="s">
+      <c r="Q28" s="91"/>
+      <c r="R28" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="S28" s="35"/>
-      <c r="T28" s="10"/>
+      <c r="S28" s="91"/>
       <c r="U28" s="5"/>
     </row>
     <row r="29" spans="1:21">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="20">
-        <v>0</v>
-      </c>
-      <c r="F29" s="20">
-        <v>0</v>
-      </c>
-      <c r="G29" s="20">
-        <v>0</v>
-      </c>
-      <c r="H29" s="20">
-        <v>0</v>
-      </c>
-      <c r="I29" s="20">
-        <v>0</v>
-      </c>
-      <c r="J29" s="20">
-        <v>0</v>
-      </c>
-      <c r="K29" s="20">
-        <v>0</v>
-      </c>
-      <c r="L29" s="20">
-        <v>0</v>
-      </c>
-      <c r="M29" s="20">
-        <v>0</v>
-      </c>
-      <c r="N29" s="20">
-        <v>0</v>
-      </c>
-      <c r="O29" s="20">
-        <v>0</v>
-      </c>
-      <c r="P29" s="29">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29">
-        <v>0</v>
-      </c>
-      <c r="S29" s="29"/>
-      <c r="T29" s="10"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="16">
+        <v>0</v>
+      </c>
+      <c r="F29" s="16">
+        <v>0</v>
+      </c>
+      <c r="G29" s="16">
+        <v>0</v>
+      </c>
+      <c r="H29" s="16">
+        <v>0</v>
+      </c>
+      <c r="I29" s="16">
+        <v>0</v>
+      </c>
+      <c r="J29" s="16">
+        <v>0</v>
+      </c>
+      <c r="K29" s="16">
+        <v>0</v>
+      </c>
+      <c r="L29" s="16">
+        <v>0</v>
+      </c>
+      <c r="M29" s="16">
+        <v>0</v>
+      </c>
+      <c r="N29" s="16">
+        <v>0</v>
+      </c>
+      <c r="O29" s="16">
+        <v>0</v>
+      </c>
+      <c r="P29" s="95">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="95"/>
+      <c r="R29" s="95">
+        <v>0</v>
+      </c>
+      <c r="S29" s="95"/>
       <c r="U29" s="5"/>
     </row>
     <row r="30" spans="1:21">
-      <c r="A30" s="39" t="s">
+      <c r="A30" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="20">
-        <v>0</v>
-      </c>
-      <c r="F30" s="20">
-        <v>0</v>
-      </c>
-      <c r="G30" s="20">
-        <v>0</v>
-      </c>
-      <c r="H30" s="20">
-        <v>0</v>
-      </c>
-      <c r="I30" s="20">
-        <v>0</v>
-      </c>
-      <c r="J30" s="20">
-        <v>0</v>
-      </c>
-      <c r="K30" s="20">
-        <v>0</v>
-      </c>
-      <c r="L30" s="20">
-        <v>0</v>
-      </c>
-      <c r="M30" s="20">
-        <v>0</v>
-      </c>
-      <c r="N30" s="20">
-        <v>0</v>
-      </c>
-      <c r="O30" s="20">
-        <v>0</v>
-      </c>
-      <c r="P30" s="29">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29">
-        <v>0</v>
-      </c>
-      <c r="S30" s="29"/>
-      <c r="T30" s="10"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="16">
+        <v>0</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0</v>
+      </c>
+      <c r="G30" s="16">
+        <v>0</v>
+      </c>
+      <c r="H30" s="16">
+        <v>0</v>
+      </c>
+      <c r="I30" s="16">
+        <v>0</v>
+      </c>
+      <c r="J30" s="16">
+        <v>0</v>
+      </c>
+      <c r="K30" s="16">
+        <v>0</v>
+      </c>
+      <c r="L30" s="16">
+        <v>0</v>
+      </c>
+      <c r="M30" s="16">
+        <v>0</v>
+      </c>
+      <c r="N30" s="16">
+        <v>0</v>
+      </c>
+      <c r="O30" s="16">
+        <v>0</v>
+      </c>
+      <c r="P30" s="95">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="95">
+        <v>0</v>
+      </c>
+      <c r="S30" s="95"/>
       <c r="U30" s="5"/>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="4"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
       <c r="U31" s="5"/>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="57" t="s">
+      <c r="A32" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="58"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="64">
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="37">
         <v>46182</v>
       </c>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="46"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="58"/>
-      <c r="Q32" s="58"/>
-      <c r="R32" s="58"/>
-      <c r="S32" s="58"/>
-      <c r="T32" s="58"/>
-      <c r="U32" s="73"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="41"/>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="60"/>
-      <c r="B33" s="61"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="65" t="s">
+      <c r="A33" s="34"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="46"/>
-      <c r="O33" s="74"/>
-      <c r="P33" s="61"/>
-      <c r="Q33" s="61"/>
-      <c r="R33" s="61"/>
-      <c r="S33" s="61"/>
-      <c r="T33" s="61"/>
-      <c r="U33" s="75"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35"/>
+      <c r="U33" s="43"/>
     </row>
     <row r="34" spans="1:21" s="2" customFormat="1">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="14" t="s">
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I34" s="13" t="s">
+      <c r="I34" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="J34" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="K34" s="63" t="s">
+      <c r="K34" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="L34" s="41"/>
-      <c r="M34" s="63" t="s">
+      <c r="L34" s="28"/>
+      <c r="M34" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="N34" s="41"/>
-      <c r="O34" s="63" t="s">
+      <c r="N34" s="28"/>
+      <c r="O34" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="41"/>
-      <c r="S34" s="63" t="s">
+      <c r="P34" s="27"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="T34" s="40"/>
-      <c r="U34" s="56"/>
+      <c r="T34" s="27"/>
+      <c r="U34" s="82"/>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="20">
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="16">
         <f>'[1]Line Stop_Prod Loss'!G5</f>
         <v>0.5</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="16">
         <f>'[1]Line Stop_Prod Loss'!H5</f>
         <v>73.7</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="16">
         <f>'[1]Line Stop_Prod Loss'!F5</f>
         <v>0</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="16">
         <f>'[1]Line Stop_Prod Loss'!E5</f>
         <v>0</v>
       </c>
-      <c r="I35" s="20">
+      <c r="I35" s="16">
         <f>'[1]Line Stop_Prod Loss'!D5</f>
         <v>0</v>
       </c>
-      <c r="J35" s="20">
+      <c r="J35" s="16">
         <f>'[1]Line Stop_Prod Loss'!C5</f>
         <v>0</v>
       </c>
-      <c r="K35" s="20">
-        <v>0</v>
-      </c>
-      <c r="L35" s="20">
-        <v>0</v>
-      </c>
-      <c r="M35" s="20">
-        <v>0</v>
-      </c>
-      <c r="N35" s="20">
-        <v>0</v>
-      </c>
-      <c r="O35" s="95" t="s">
+      <c r="K35" s="16">
+        <v>0</v>
+      </c>
+      <c r="L35" s="16">
+        <v>0</v>
+      </c>
+      <c r="M35" s="16">
+        <v>0</v>
+      </c>
+      <c r="N35" s="16">
+        <v>0</v>
+      </c>
+      <c r="O35" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="P35" s="40"/>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="41"/>
-      <c r="S35" s="96"/>
-      <c r="T35" s="40"/>
-      <c r="U35" s="56"/>
+      <c r="P35" s="27"/>
+      <c r="Q35" s="27"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="81"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="82"/>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="44" t="s">
+      <c r="A36" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="46"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="8">
         <f>'[1]Line Stop_Prod Loss'!G6</f>
         <v>156.30000000000001</v>
@@ -3878,23 +3792,23 @@
       <c r="N36" s="8">
         <v>0</v>
       </c>
-      <c r="O36" s="95" t="s">
+      <c r="O36" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="96"/>
-      <c r="T36" s="40"/>
-      <c r="U36" s="56"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="81"/>
+      <c r="T36" s="27"/>
+      <c r="U36" s="82"/>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="44" t="s">
+      <c r="A37" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="45"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="46"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="8">
         <f>'[1]Line Stop_Prod Loss'!G7</f>
         <v>0</v>
@@ -3931,21 +3845,21 @@
       <c r="N37" s="8">
         <v>0</v>
       </c>
-      <c r="O37" s="95"/>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="40"/>
-      <c r="R37" s="41"/>
-      <c r="S37" s="96"/>
-      <c r="T37" s="40"/>
-      <c r="U37" s="56"/>
+      <c r="O37" s="83"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="81"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="82"/>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="44" t="s">
+      <c r="A38" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="46"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="8">
         <f>'[1]Line Stop_Prod Loss'!G8</f>
         <v>0.1</v>
@@ -3982,66 +3896,66 @@
       <c r="N38" s="8">
         <v>0</v>
       </c>
-      <c r="O38" s="95" t="s">
+      <c r="O38" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="40"/>
-      <c r="R38" s="41"/>
-      <c r="S38" s="96"/>
-      <c r="T38" s="40"/>
-      <c r="U38" s="56"/>
-    </row>
-    <row r="39" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A39" s="97" t="s">
+      <c r="P38" s="27"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="81"/>
+      <c r="T38" s="27"/>
+      <c r="U38" s="82"/>
+    </row>
+    <row r="39" spans="1:21" ht="15" thickBot="1">
+      <c r="A39" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="26">
+      <c r="B39" s="87"/>
+      <c r="C39" s="87"/>
+      <c r="D39" s="88"/>
+      <c r="E39" s="22">
         <f>'[1]Line Stop_Prod Loss'!G9</f>
         <v>0</v>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="22">
         <f>'[1]Line Stop_Prod Loss'!H9</f>
         <v>0</v>
       </c>
-      <c r="G39" s="26">
+      <c r="G39" s="22">
         <f>'[1]Line Stop_Prod Loss'!F9</f>
         <v>0</v>
       </c>
-      <c r="H39" s="26">
+      <c r="H39" s="22">
         <f>'[1]Line Stop_Prod Loss'!E9</f>
         <v>0</v>
       </c>
-      <c r="I39" s="26">
+      <c r="I39" s="22">
         <f>'[1]Line Stop_Prod Loss'!D9</f>
         <v>0</v>
       </c>
-      <c r="J39" s="26">
+      <c r="J39" s="22">
         <f>'[1]Line Stop_Prod Loss'!C9</f>
         <v>0</v>
       </c>
-      <c r="K39" s="26">
-        <v>0</v>
-      </c>
-      <c r="L39" s="26">
-        <v>0</v>
-      </c>
-      <c r="M39" s="26">
-        <v>0</v>
-      </c>
-      <c r="N39" s="26">
-        <v>0</v>
-      </c>
-      <c r="O39" s="98"/>
-      <c r="P39" s="68"/>
-      <c r="Q39" s="68"/>
-      <c r="R39" s="71"/>
-      <c r="S39" s="99"/>
-      <c r="T39" s="68"/>
-      <c r="U39" s="69"/>
+      <c r="K39" s="22">
+        <v>0</v>
+      </c>
+      <c r="L39" s="22">
+        <v>0</v>
+      </c>
+      <c r="M39" s="22">
+        <v>0</v>
+      </c>
+      <c r="N39" s="22">
+        <v>0</v>
+      </c>
+      <c r="O39" s="55"/>
+      <c r="P39" s="52"/>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="56"/>
+      <c r="S39" s="51"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="53"/>
     </row>
     <row r="40" spans="1:21">
       <c r="L40" s="1"/>
@@ -4049,18 +3963,78 @@
     <row r="41" spans="1:21" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="111">
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A32:D33"/>
-    <mergeCell ref="E32:N32"/>
-    <mergeCell ref="O32:U33"/>
-    <mergeCell ref="E33:N33"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="S34:U34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="O35:R35"/>
+    <mergeCell ref="S35:U35"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A23:S23"/>
+    <mergeCell ref="A24:D25"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="H24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="F2:L3"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="S39:U39"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="O39:R39"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A6:S6"/>
+    <mergeCell ref="A7:D8"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="S38:U38"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="S37:U37"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="S36:U36"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:R34"/>
     <mergeCell ref="R8:S8"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
@@ -4076,78 +4050,21 @@
     <mergeCell ref="M17:O17"/>
     <mergeCell ref="P17:Q17"/>
     <mergeCell ref="R17:S17"/>
-    <mergeCell ref="S39:U39"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A6:S6"/>
-    <mergeCell ref="A7:D8"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="F2:L3"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:L8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="S38:U38"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="S37:U37"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="S36:U36"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:R34"/>
-    <mergeCell ref="S34:U34"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="O35:R35"/>
-    <mergeCell ref="S35:U35"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A23:S23"/>
-    <mergeCell ref="A24:D25"/>
-    <mergeCell ref="E24:G24"/>
     <mergeCell ref="P9:Q9"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="H24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A32:D33"/>
+    <mergeCell ref="E32:N32"/>
+    <mergeCell ref="O32:U33"/>
+    <mergeCell ref="E33:N33"/>
     <mergeCell ref="R28:S28"/>
     <mergeCell ref="P29:Q29"/>
     <mergeCell ref="R29:S29"/>
@@ -4157,9 +4074,6 @@
     <mergeCell ref="R26:S26"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="R27:S27"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="R21:S21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="49" orientation="landscape" r:id="rId1"/>
@@ -4172,11 +4086,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:M32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="12" max="12" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">

--- a/Eka_Report_back/ProductionReport_R3.xlsx
+++ b/Eka_Report_back/ProductionReport_R3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eka_Report\Eka_Report\Eka_Report_back\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A449D1-7492-465C-8D45-24BFC10A5531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41F6072-A4E6-4CEE-92A6-D6D7EA3CB352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3480" yWindow="1560" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prod Report" sheetId="1" r:id="rId1"/>
@@ -340,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T10" authorId="1" shapeId="0" xr:uid="{ACB9D69B-27C1-4F26-954C-6F98F32C0484}">
+    <comment ref="D19" authorId="1" shapeId="0" xr:uid="{2DA04D93-327A-4BE2-853F-93D18F92A10F}">
       <text>
         <r>
           <rPr>
@@ -353,7 +353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D19" authorId="1" shapeId="0" xr:uid="{2DA04D93-327A-4BE2-853F-93D18F92A10F}">
+    <comment ref="E19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -366,7 +366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="F19" authorId="1" shapeId="0" xr:uid="{3BC78DD6-CAB0-4EBB-884F-98AB8C469DA5}">
       <text>
         <r>
           <rPr>
@@ -379,7 +379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F19" authorId="1" shapeId="0" xr:uid="{3BC78DD6-CAB0-4EBB-884F-98AB8C469DA5}">
+    <comment ref="G19" authorId="1" shapeId="0" xr:uid="{93EB86C2-A544-497A-8D76-C02B4F9E343E}">
       <text>
         <r>
           <rPr>
@@ -392,7 +392,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="G19" authorId="1" shapeId="0" xr:uid="{93EB86C2-A544-497A-8D76-C02B4F9E343E}">
+    <comment ref="M19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t>DELL:
+Last shift value of day</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t>DELL:
+last actual value of day</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P19" authorId="1" shapeId="0" xr:uid="{00EBCB6E-1718-43E9-8930-A9EF37AB34E9}">
       <text>
         <r>
           <rPr>
@@ -405,33 +431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>DELL:
-Last shift value of day</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>DELL:
-last actual value of day</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P19" authorId="1" shapeId="0" xr:uid="{00EBCB6E-1718-43E9-8930-A9EF37AB34E9}">
+    <comment ref="Q19" authorId="1" shapeId="0" xr:uid="{F70F0108-FFE2-4C0A-AC58-2F53C2890546}">
       <text>
         <r>
           <rPr>
@@ -444,7 +444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="1" shapeId="0" xr:uid="{F70F0108-FFE2-4C0A-AC58-2F53C2890546}">
+    <comment ref="R19" authorId="1" shapeId="0" xr:uid="{B1220148-802A-4884-9B2E-A91ABC605F1F}">
       <text>
         <r>
           <rPr>
@@ -457,33 +457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="1" shapeId="0" xr:uid="{B1220148-802A-4884-9B2E-A91ABC605F1F}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>DELL:
-days total</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="S19" authorId="1" shapeId="0" xr:uid="{3AD3EEA6-8D92-4D15-B2B7-ED0A69FE6C25}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="SimSun"/>
-            <charset val="134"/>
-          </rPr>
-          <t>DELL:
-days total</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T19" authorId="1" shapeId="0" xr:uid="{735402FA-347E-4A09-B8F4-E3085254907E}">
       <text>
         <r>
           <rPr>
@@ -1200,12 +1174,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="64">
   <si>
     <t>Date</t>
-  </si>
-  <si>
-    <t>10-06-2026</t>
   </si>
   <si>
     <t>MANAGEMENT PRODUCTION REPORT</t>
@@ -1519,7 +1490,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1939,11 +1910,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2002,6 +1986,209 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="18" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2011,218 +2198,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="18" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2718,100 +2711,100 @@
     <row r="2" spans="1:22" ht="15" customHeight="1">
       <c r="A2" s="19"/>
       <c r="B2" s="26"/>
-      <c r="C2" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="65" t="s">
+      <c r="C2" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="51"/>
+      <c r="E2" s="31">
+        <v>0</v>
+      </c>
+      <c r="F2" s="32"/>
+      <c r="G2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="66"/>
-      <c r="G2" s="84" t="s">
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="73" t="s">
-        <v>3</v>
-      </c>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="75"/>
-      <c r="U2" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="V2" s="68"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" s="34"/>
     </row>
     <row r="3" spans="1:22" ht="15" customHeight="1">
       <c r="A3" s="3"/>
       <c r="B3" s="24"/>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="53"/>
+      <c r="E3" s="35">
+        <v>0</v>
+      </c>
+      <c r="F3" s="36"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="69">
-        <v>0.62290305717592598</v>
-      </c>
-      <c r="F3" s="70"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="76" t="s">
-        <v>6</v>
-      </c>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="71">
-        <v>26</v>
-      </c>
-      <c r="V3" s="72"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="37">
+        <v>0</v>
+      </c>
+      <c r="V3" s="38"/>
     </row>
     <row r="4" spans="1:22" ht="15.75" customHeight="1">
       <c r="A4" s="27"/>
       <c r="B4" s="25"/>
-      <c r="C4" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="107">
-        <v>46181</v>
-      </c>
-      <c r="F4" s="108"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="91"/>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="76" t="s">
-        <v>7</v>
-      </c>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="78"/>
-      <c r="U4" s="71">
-        <v>18</v>
-      </c>
-      <c r="V4" s="72"/>
+      <c r="C4" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="54"/>
+      <c r="E4" s="48">
+        <v>0</v>
+      </c>
+      <c r="F4" s="49"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="37">
+        <v>0</v>
+      </c>
+      <c r="V4" s="38"/>
     </row>
     <row r="5" spans="1:22" ht="15" thickBot="1">
       <c r="A5" s="20"/>
@@ -2838,357 +2831,351 @@
       <c r="V5" s="23"/>
     </row>
     <row r="6" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A6" s="60" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="62"/>
+      <c r="A6" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="41"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="37"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="38" t="s">
+      <c r="A7" s="108"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="38" t="s">
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38" t="s">
+      <c r="N7" s="65"/>
+      <c r="O7" s="65"/>
+      <c r="P7" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="106" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q7" s="106"/>
-      <c r="R7" s="106"/>
-      <c r="S7" s="38" t="s">
+      <c r="T7" s="65"/>
+      <c r="U7" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="T7" s="94"/>
-      <c r="U7" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="V7" s="95"/>
+      <c r="V7" s="66"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="38" t="s">
+      <c r="A8" s="106"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="40" t="s">
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="94"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q8" s="94"/>
-      <c r="R8" s="94"/>
-      <c r="S8" s="40" t="s">
+      <c r="T8" s="65"/>
+      <c r="U8" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="T8" s="94"/>
-      <c r="U8" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="V8" s="95"/>
+      <c r="V8" s="66"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="89" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="J9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="K9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="L9" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="O9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="8" t="s">
-        <v>21</v>
-      </c>
       <c r="P9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="R9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="S9" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="T9" s="94"/>
-      <c r="U9" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="V9" s="95"/>
+      <c r="S9" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="T9" s="65"/>
+      <c r="U9" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="V9" s="66"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="93" t="s">
-        <v>33</v>
+      <c r="A10" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="28" t="s">
+        <v>32</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="T10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="U10" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="V10" s="95"/>
+        <v>32</v>
+      </c>
+      <c r="S10" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" s="109"/>
+      <c r="U10" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="V10" s="66"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="93" t="s">
-        <v>33</v>
+      <c r="A11" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="28" t="s">
+        <v>32</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="T11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="U11" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="V11" s="95"/>
+        <v>32</v>
+      </c>
+      <c r="S11" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="109"/>
+      <c r="U11" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="V11" s="66"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="93" t="s">
-        <v>33</v>
+      <c r="A12" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="28" t="s">
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="T12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="U12" s="45">
-        <v>0</v>
-      </c>
-      <c r="V12" s="95"/>
+        <v>32</v>
+      </c>
+      <c r="S12" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12" s="109"/>
+      <c r="U12" s="73">
+        <v>0</v>
+      </c>
+      <c r="V12" s="66"/>
     </row>
     <row r="13" spans="1:22" ht="15" thickBot="1">
-      <c r="A13" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="98" t="s">
-        <v>33</v>
+      <c r="A13" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="29" t="s">
+        <v>32</v>
       </c>
       <c r="E13" s="16">
         <v>0</v>
@@ -3232,16 +3219,14 @@
       <c r="R13" s="16">
         <v>0</v>
       </c>
-      <c r="S13" s="16">
-        <v>0</v>
-      </c>
-      <c r="T13" s="16">
-        <v>0</v>
-      </c>
-      <c r="U13" s="47">
-        <v>0</v>
-      </c>
-      <c r="V13" s="97"/>
+      <c r="S13" s="110" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" s="111"/>
+      <c r="U13" s="76">
+        <v>0</v>
+      </c>
+      <c r="V13" s="77"/>
     </row>
     <row r="14" spans="1:22" ht="15" thickBot="1">
       <c r="A14" s="3"/>
@@ -3251,169 +3236,169 @@
       <c r="V14" s="5"/>
     </row>
     <row r="15" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A15" s="60" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="61"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="61"/>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="61"/>
-      <c r="T15" s="61"/>
-      <c r="U15" s="61"/>
-      <c r="V15" s="62"/>
+      <c r="A15" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="41"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="36"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="38" t="s">
+      <c r="A16" s="107"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="38" t="s">
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38" t="s">
+      <c r="N16" s="65"/>
+      <c r="O16" s="65"/>
+      <c r="P16" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="N16" s="94"/>
-      <c r="O16" s="94"/>
-      <c r="P16" s="106" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q16" s="106"/>
-      <c r="R16" s="106"/>
-      <c r="S16" s="38" t="s">
+      <c r="T16" s="65"/>
+      <c r="U16" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="T16" s="94"/>
-      <c r="U16" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="V16" s="95"/>
+      <c r="V16" s="66"/>
     </row>
     <row r="17" spans="1:22">
-      <c r="A17" s="34"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="38" t="s">
+      <c r="A17" s="106"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="40" t="s">
+      <c r="N17" s="65"/>
+      <c r="O17" s="65"/>
+      <c r="P17" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="N17" s="94"/>
-      <c r="O17" s="94"/>
-      <c r="P17" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q17" s="94"/>
-      <c r="R17" s="94"/>
-      <c r="S17" s="40" t="s">
+      <c r="T17" s="65"/>
+      <c r="U17" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="T17" s="94"/>
-      <c r="U17" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="V17" s="95"/>
+      <c r="V17" s="66"/>
     </row>
     <row r="18" spans="1:22">
-      <c r="A18" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
+      <c r="A18" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
       <c r="D18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="I18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="J18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="K18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="L18" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N18" s="8" t="s">
+      <c r="O18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O18" s="8" t="s">
-        <v>21</v>
-      </c>
       <c r="P18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q18" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Q18" s="8" t="s">
+      <c r="R18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="S18" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="T18" s="94"/>
-      <c r="U18" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="V18" s="95"/>
+      <c r="S18" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" s="65"/>
+      <c r="U18" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="V18" s="66"/>
     </row>
     <row r="19" spans="1:22">
-      <c r="A19" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
+      <c r="A19" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
       <c r="D19" s="6">
         <v>0</v>
       </c>
@@ -3459,23 +3444,21 @@
       <c r="R19" s="6">
         <v>0</v>
       </c>
-      <c r="S19" s="6">
-        <v>0</v>
-      </c>
-      <c r="T19" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="U19" s="103" t="s">
-        <v>33</v>
-      </c>
-      <c r="V19" s="104"/>
+      <c r="S19" s="79">
+        <v>0</v>
+      </c>
+      <c r="T19" s="109"/>
+      <c r="U19" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="V19" s="80"/>
     </row>
     <row r="20" spans="1:22">
-      <c r="A20" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
+      <c r="A20" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
       <c r="D20" s="6">
         <v>0</v>
       </c>
@@ -3521,33 +3504,31 @@
       <c r="R20" s="6">
         <v>0</v>
       </c>
-      <c r="S20" s="6">
-        <v>0</v>
-      </c>
-      <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="101" t="s">
-        <v>33</v>
-      </c>
-      <c r="V20" s="102"/>
+      <c r="S20" s="79">
+        <v>0</v>
+      </c>
+      <c r="T20" s="109"/>
+      <c r="U20" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="V20" s="82"/>
     </row>
     <row r="21" spans="1:22" ht="15" thickBot="1">
-      <c r="A21" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="105">
-        <v>0</v>
-      </c>
-      <c r="E21" s="105">
-        <v>0</v>
-      </c>
-      <c r="F21" s="105">
-        <v>0</v>
-      </c>
-      <c r="G21" s="105">
+      <c r="A21" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="30">
+        <v>0</v>
+      </c>
+      <c r="E21" s="30">
+        <v>0</v>
+      </c>
+      <c r="F21" s="30">
+        <v>0</v>
+      </c>
+      <c r="G21" s="30">
         <v>0</v>
       </c>
       <c r="H21" s="16">
@@ -3574,25 +3555,23 @@
       <c r="O21" s="16">
         <v>0</v>
       </c>
-      <c r="P21" s="105">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="105">
-        <v>0</v>
-      </c>
-      <c r="R21" s="105">
-        <v>0</v>
-      </c>
-      <c r="S21" s="105">
-        <v>0</v>
-      </c>
-      <c r="T21" s="105">
-        <v>0</v>
-      </c>
-      <c r="U21" s="99">
-        <v>0</v>
-      </c>
-      <c r="V21" s="100"/>
+      <c r="P21" s="30">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="30">
+        <v>0</v>
+      </c>
+      <c r="R21" s="30">
+        <v>0</v>
+      </c>
+      <c r="S21" s="110">
+        <v>0</v>
+      </c>
+      <c r="T21" s="111"/>
+      <c r="U21" s="84">
+        <v>0</v>
+      </c>
+      <c r="V21" s="85"/>
     </row>
     <row r="22" spans="1:22" ht="15" thickBot="1">
       <c r="A22" s="11"/>
@@ -3618,289 +3597,289 @@
       <c r="V22" s="5"/>
     </row>
     <row r="23" spans="1:22" ht="15.6" customHeight="1">
-      <c r="A23" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="61"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="61"/>
-      <c r="R23" s="61"/>
-      <c r="S23" s="61"/>
-      <c r="T23" s="61"/>
-      <c r="U23" s="61"/>
-      <c r="V23" s="62"/>
+      <c r="A23" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="40"/>
+      <c r="S23" s="40"/>
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="41"/>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="36"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="94"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="38" t="s">
+      <c r="A24" s="107"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38" t="s">
+      <c r="N24" s="65"/>
+      <c r="O24" s="65"/>
+      <c r="P24" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="N24" s="94"/>
-      <c r="O24" s="94"/>
-      <c r="P24" s="106" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q24" s="106"/>
-      <c r="R24" s="106"/>
-      <c r="S24" s="38" t="s">
+      <c r="T24" s="65"/>
+      <c r="U24" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="T24" s="94"/>
-      <c r="U24" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="V24" s="95"/>
+      <c r="V24" s="66"/>
     </row>
     <row r="25" spans="1:22">
-      <c r="A25" s="34"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="94"/>
-      <c r="F25" s="94"/>
-      <c r="G25" s="38" t="s">
+      <c r="A25" s="106"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
+      <c r="K25" s="64"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="40" t="s">
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="N25" s="94"/>
-      <c r="O25" s="94"/>
-      <c r="P25" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q25" s="94"/>
-      <c r="R25" s="94"/>
-      <c r="S25" s="40" t="s">
+      <c r="T25" s="65"/>
+      <c r="U25" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="T25" s="94"/>
-      <c r="U25" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="V25" s="95"/>
+      <c r="V25" s="66"/>
     </row>
     <row r="26" spans="1:22">
-      <c r="A26" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
+      <c r="A26" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
       <c r="D26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="F26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="G26" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="H26" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="I26" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="J26" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="K26" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K26" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="L26" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N26" s="8" t="s">
+      <c r="O26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="O26" s="8" t="s">
-        <v>21</v>
-      </c>
       <c r="P26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q26" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Q26" s="8" t="s">
+      <c r="R26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="R26" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="S26" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="T26" s="94"/>
-      <c r="U26" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="V26" s="95"/>
+      <c r="S26" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="T26" s="65"/>
+      <c r="U26" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="V26" s="66"/>
     </row>
     <row r="27" spans="1:22">
-      <c r="A27" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
+      <c r="A27" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
       <c r="D27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S27" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="T27" s="94"/>
-      <c r="U27" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="V27" s="95"/>
+        <v>32</v>
+      </c>
+      <c r="S27" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="T27" s="65"/>
+      <c r="U27" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="V27" s="66"/>
     </row>
     <row r="28" spans="1:22">
-      <c r="A28" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
+      <c r="A28" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
       <c r="D28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S28" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="T28" s="94"/>
-      <c r="U28" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="V28" s="95"/>
+        <v>32</v>
+      </c>
+      <c r="S28" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="T28" s="65"/>
+      <c r="U28" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="V28" s="66"/>
     </row>
     <row r="29" spans="1:22">
-      <c r="A29" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
+      <c r="A29" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="68"/>
+      <c r="C29" s="68"/>
       <c r="D29" s="7">
         <v>0</v>
       </c>
@@ -3946,21 +3925,21 @@
       <c r="R29" s="7">
         <v>0</v>
       </c>
-      <c r="S29" s="45">
-        <v>0</v>
-      </c>
-      <c r="T29" s="94"/>
-      <c r="U29" s="45">
-        <v>0</v>
-      </c>
-      <c r="V29" s="95"/>
+      <c r="S29" s="73">
+        <v>0</v>
+      </c>
+      <c r="T29" s="65"/>
+      <c r="U29" s="73">
+        <v>0</v>
+      </c>
+      <c r="V29" s="66"/>
     </row>
     <row r="30" spans="1:22" ht="15" thickBot="1">
-      <c r="A30" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
+      <c r="A30" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="75"/>
+      <c r="C30" s="75"/>
       <c r="D30" s="16">
         <v>0</v>
       </c>
@@ -4006,14 +3985,14 @@
       <c r="R30" s="16">
         <v>0</v>
       </c>
-      <c r="S30" s="47">
-        <v>0</v>
-      </c>
-      <c r="T30" s="96"/>
-      <c r="U30" s="47">
-        <v>0</v>
-      </c>
-      <c r="V30" s="97"/>
+      <c r="S30" s="76">
+        <v>0</v>
+      </c>
+      <c r="T30" s="87"/>
+      <c r="U30" s="76">
+        <v>0</v>
+      </c>
+      <c r="V30" s="77"/>
     </row>
     <row r="31" spans="1:22" ht="15" thickBot="1">
       <c r="A31" s="3"/>
@@ -4027,111 +4006,111 @@
       <c r="V31" s="5"/>
     </row>
     <row r="32" spans="1:22">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="50"/>
-      <c r="P32" s="50"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50"/>
-      <c r="S32" s="50"/>
-      <c r="T32" s="50"/>
-      <c r="U32" s="50"/>
-      <c r="V32" s="52"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="92"/>
+      <c r="N32" s="92"/>
+      <c r="O32" s="92"/>
+      <c r="P32" s="92"/>
+      <c r="Q32" s="92"/>
+      <c r="R32" s="92"/>
+      <c r="S32" s="92"/>
+      <c r="T32" s="92"/>
+      <c r="U32" s="92"/>
+      <c r="V32" s="94"/>
     </row>
     <row r="33" spans="1:22">
-      <c r="A33" s="34"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
-      <c r="V33" s="54"/>
+      <c r="A33" s="106"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="95"/>
+      <c r="O33" s="95"/>
+      <c r="P33" s="95"/>
+      <c r="Q33" s="95"/>
+      <c r="R33" s="95"/>
+      <c r="S33" s="95"/>
+      <c r="T33" s="95"/>
+      <c r="U33" s="95"/>
+      <c r="V33" s="96"/>
     </row>
     <row r="34" spans="1:22" s="1" customFormat="1" ht="28.8">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="89" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="90"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="G34" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="H34" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="J34" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="H34" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="I34" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="J34" s="18" t="s">
+      <c r="K34" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="K34" s="17" t="s">
+      <c r="L34" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="L34" s="38" t="s">
+      <c r="M34" s="64"/>
+      <c r="N34" s="64"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="64"/>
+      <c r="S34" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
-      <c r="R34" s="38"/>
-      <c r="S34" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="T34" s="38"/>
-      <c r="U34" s="38"/>
-      <c r="V34" s="55"/>
+      <c r="T34" s="64"/>
+      <c r="U34" s="64"/>
+      <c r="V34" s="97"/>
     </row>
     <row r="35" spans="1:22">
-      <c r="A35" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="35"/>
+      <c r="A35" s="88" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
       <c r="D35" s="7">
         <v>0</v>
       </c>
@@ -4156,24 +4135,24 @@
       <c r="K35" s="7">
         <v>0</v>
       </c>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="43"/>
-      <c r="Q35" s="43"/>
-      <c r="R35" s="43"/>
-      <c r="S35" s="43"/>
-      <c r="T35" s="43"/>
-      <c r="U35" s="43"/>
-      <c r="V35" s="56"/>
+      <c r="L35" s="91"/>
+      <c r="M35" s="91"/>
+      <c r="N35" s="91"/>
+      <c r="O35" s="91"/>
+      <c r="P35" s="91"/>
+      <c r="Q35" s="91"/>
+      <c r="R35" s="91"/>
+      <c r="S35" s="91"/>
+      <c r="T35" s="91"/>
+      <c r="U35" s="91"/>
+      <c r="V35" s="98"/>
     </row>
     <row r="36" spans="1:22">
-      <c r="A36" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="35"/>
-      <c r="C36" s="35"/>
+      <c r="A36" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="68"/>
+      <c r="C36" s="68"/>
       <c r="D36" s="7">
         <v>0</v>
       </c>
@@ -4198,24 +4177,24 @@
       <c r="K36" s="7">
         <v>0</v>
       </c>
-      <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="43"/>
-      <c r="R36" s="43"/>
-      <c r="S36" s="57"/>
-      <c r="T36" s="57"/>
-      <c r="U36" s="57"/>
-      <c r="V36" s="58"/>
+      <c r="L36" s="91"/>
+      <c r="M36" s="91"/>
+      <c r="N36" s="91"/>
+      <c r="O36" s="91"/>
+      <c r="P36" s="91"/>
+      <c r="Q36" s="91"/>
+      <c r="R36" s="91"/>
+      <c r="S36" s="99"/>
+      <c r="T36" s="99"/>
+      <c r="U36" s="99"/>
+      <c r="V36" s="100"/>
     </row>
     <row r="37" spans="1:22">
-      <c r="A37" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" s="35"/>
-      <c r="C37" s="35"/>
+      <c r="A37" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" s="68"/>
+      <c r="C37" s="68"/>
       <c r="D37" s="7">
         <v>0</v>
       </c>
@@ -4240,24 +4219,24 @@
       <c r="K37" s="7">
         <v>0</v>
       </c>
-      <c r="L37" s="43"/>
-      <c r="M37" s="43"/>
-      <c r="N37" s="43"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="43"/>
-      <c r="Q37" s="43"/>
-      <c r="R37" s="43"/>
-      <c r="S37" s="43"/>
-      <c r="T37" s="43"/>
-      <c r="U37" s="43"/>
-      <c r="V37" s="56"/>
+      <c r="L37" s="91"/>
+      <c r="M37" s="91"/>
+      <c r="N37" s="91"/>
+      <c r="O37" s="91"/>
+      <c r="P37" s="91"/>
+      <c r="Q37" s="91"/>
+      <c r="R37" s="91"/>
+      <c r="S37" s="91"/>
+      <c r="T37" s="91"/>
+      <c r="U37" s="91"/>
+      <c r="V37" s="98"/>
     </row>
     <row r="38" spans="1:22">
-      <c r="A38" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="35"/>
-      <c r="C38" s="35"/>
+      <c r="A38" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
       <c r="D38" s="7">
         <v>0</v>
       </c>
@@ -4282,63 +4261,63 @@
       <c r="K38" s="7">
         <v>0</v>
       </c>
-      <c r="L38" s="43"/>
-      <c r="M38" s="43"/>
-      <c r="N38" s="43"/>
-      <c r="O38" s="43"/>
-      <c r="P38" s="43"/>
-      <c r="Q38" s="43"/>
-      <c r="R38" s="43"/>
-      <c r="S38" s="43"/>
-      <c r="T38" s="43"/>
-      <c r="U38" s="43"/>
-      <c r="V38" s="56"/>
+      <c r="L38" s="91"/>
+      <c r="M38" s="91"/>
+      <c r="N38" s="91"/>
+      <c r="O38" s="91"/>
+      <c r="P38" s="91"/>
+      <c r="Q38" s="91"/>
+      <c r="R38" s="91"/>
+      <c r="S38" s="91"/>
+      <c r="T38" s="91"/>
+      <c r="U38" s="91"/>
+      <c r="V38" s="98"/>
     </row>
     <row r="39" spans="1:22" ht="15" customHeight="1" thickBot="1">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="103" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="75"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="16">
+        <v>0</v>
+      </c>
+      <c r="E39" s="16">
+        <v>0</v>
+      </c>
+      <c r="F39" s="16">
+        <v>0</v>
+      </c>
+      <c r="G39" s="16">
+        <v>0</v>
+      </c>
+      <c r="H39" s="16">
+        <v>0</v>
+      </c>
+      <c r="I39" s="16">
+        <v>0</v>
+      </c>
+      <c r="J39" s="16">
+        <v>0</v>
+      </c>
+      <c r="K39" s="16">
+        <v>0</v>
+      </c>
+      <c r="L39" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="16">
-        <v>0</v>
-      </c>
-      <c r="E39" s="16">
-        <v>0</v>
-      </c>
-      <c r="F39" s="16">
-        <v>0</v>
-      </c>
-      <c r="G39" s="16">
-        <v>0</v>
-      </c>
-      <c r="H39" s="16">
-        <v>0</v>
-      </c>
-      <c r="I39" s="16">
-        <v>0</v>
-      </c>
-      <c r="J39" s="16">
-        <v>0</v>
-      </c>
-      <c r="K39" s="16">
-        <v>0</v>
-      </c>
-      <c r="L39" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="29"/>
+      <c r="M39" s="101"/>
+      <c r="N39" s="101"/>
+      <c r="O39" s="101"/>
+      <c r="P39" s="101"/>
+      <c r="Q39" s="101"/>
+      <c r="R39" s="101"/>
+      <c r="S39" s="101" t="s">
+        <v>48</v>
+      </c>
+      <c r="T39" s="101"/>
+      <c r="U39" s="101"/>
+      <c r="V39" s="102"/>
     </row>
     <row r="40" spans="1:22">
       <c r="K40" s="4"/>
@@ -4346,95 +4325,7 @@
     </row>
     <row r="41" spans="1:22" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="112">
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="A6:V6"/>
-    <mergeCell ref="Q2:T2"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G2:P4"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="A15:V15"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="A23:V23"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="P25:R25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="L34:R34"/>
-    <mergeCell ref="L35:R35"/>
-    <mergeCell ref="D32:K32"/>
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="L32:V33"/>
-    <mergeCell ref="S34:V34"/>
-    <mergeCell ref="S35:V35"/>
-    <mergeCell ref="S36:V36"/>
-    <mergeCell ref="S37:V37"/>
-    <mergeCell ref="S38:V38"/>
+  <mergeCells count="119">
     <mergeCell ref="S39:V39"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A32:C33"/>
@@ -4459,6 +4350,101 @@
     <mergeCell ref="S28:T28"/>
     <mergeCell ref="U28:V28"/>
     <mergeCell ref="A29:C29"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="L34:R34"/>
+    <mergeCell ref="L35:R35"/>
+    <mergeCell ref="D32:K32"/>
+    <mergeCell ref="D33:K33"/>
+    <mergeCell ref="L32:V33"/>
+    <mergeCell ref="S34:V34"/>
+    <mergeCell ref="S35:V35"/>
+    <mergeCell ref="S36:V36"/>
+    <mergeCell ref="S37:V37"/>
+    <mergeCell ref="S38:V38"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="A23:V23"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="A15:V15"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="A6:V6"/>
+    <mergeCell ref="Q2:T2"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G2:P4"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4482,12 +4468,12 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="2:13">
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -4523,12 +4509,12 @@
     <row r="3" spans="2:13"/>
     <row r="11" spans="2:13">
       <c r="B11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="2:13">
       <c r="C12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -4564,12 +4550,12 @@
     <row r="13" spans="2:13"/>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="2:13">
       <c r="C21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4605,12 +4591,12 @@
     <row r="22" spans="2:13"/>
     <row r="30" spans="2:13">
       <c r="B30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="2:13">
       <c r="C31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31">
         <v>0</v>
